--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/TownNpc.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/TownNpc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA4CC4E-F1F7-4B76-A31B-CE1D847E1F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B0685F-B590-4533-9D50-7D08E0B9B2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7510" yWindow="5320" windowWidth="51320" windowHeight="15840" xr2:uid="{9F712641-659B-4C8B-BE27-B5227352262B}"/>
+    <workbookView xWindow="0" yWindow="5040" windowWidth="51320" windowHeight="15840" xr2:uid="{9F712641-659B-4C8B-BE27-B5227352262B}"/>
   </bookViews>
   <sheets>
     <sheet name="TownNpc" sheetId="1" r:id="rId1"/>
@@ -116,9 +116,11 @@
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Character/1/0Common/Prefab/Skeleton/106011_NpcTown.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Character/2/0Common/Prefab/Skeleton/100211_NpcTown.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -176,7 +178,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -640,15 +642,15 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>-3.63</v>
       </c>
       <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5" t="s">
+        <v>-1</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>24</v>
       </c>
     </row>
@@ -663,15 +665,15 @@
         <v>23</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>-6.08</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>-3.77</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="1" t="s">
         <v>25</v>
       </c>
     </row>
